--- a/src/staticfiles/study/templates/crf_validation_rules_import_template.xlsx
+++ b/src/staticfiles/study/templates/crf_validation_rules_import_template.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -440,45 +440,40 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Form Code</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Form Code</t>
+          <t>Field Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Field Name</t>
+          <t>Rule Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Rule Type</t>
+          <t>Expression</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Expression</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Mode</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mode</t>
+          <t>Vi Message</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Vi Message</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>En Message</t>
         </is>
